--- a/24网络技术4班考勤.xlsx
+++ b/24网络技术4班考勤.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gjs\Documents\教学\最新_2025-2026第二学期\教学\4班\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\2026\教学\4班\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9180"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="考勤" sheetId="3" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="114">
   <si>
     <t>学号</t>
   </si>
@@ -578,7 +578,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -658,7 +658,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -934,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BL67"/>
+  <dimension ref="A1:BM67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.75" customWidth="1"/>
@@ -958,6 +957,9 @@
       <c r="D2">
         <v>3.06</v>
       </c>
+      <c r="E2">
+        <v>3.07</v>
+      </c>
       <c r="O2" s="25"/>
       <c r="AF2" s="26"/>
       <c r="AH2" s="26"/>
@@ -971,9 +973,12 @@
       </c>
       <c r="C3">
         <f>100-COUNTIF(D3:AZ3,"×")*3</f>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -986,10 +991,13 @@
       </c>
       <c r="C4">
         <f t="shared" ref="C4:C63" si="0">100-COUNTIF(D4:AZ4,"×")*3</f>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.2">
@@ -1001,10 +1009,13 @@
       </c>
       <c r="C5">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
         <v>6</v>
+      </c>
+      <c r="E5" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.2">
@@ -1016,10 +1027,13 @@
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
+      </c>
+      <c r="E6" t="s">
+        <v>4</v>
       </c>
       <c r="Y6" s="26"/>
     </row>
@@ -1032,10 +1046,13 @@
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
         <v>6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.2">
@@ -1047,9 +1064,12 @@
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1062,10 +1082,13 @@
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
         <v>6</v>
+      </c>
+      <c r="E9" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.2">
@@ -1077,9 +1100,12 @@
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1097,6 +1123,9 @@
       <c r="D11" t="s">
         <v>6</v>
       </c>
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A12" s="22">
@@ -1107,9 +1136,12 @@
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1127,6 +1159,9 @@
       <c r="D13" t="s">
         <v>6</v>
       </c>
+      <c r="E13" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A14" s="22">
@@ -1137,9 +1172,12 @@
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1157,6 +1195,9 @@
       <c r="D15" t="s">
         <v>6</v>
       </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A16" s="20">
@@ -1172,6 +1213,9 @@
       <c r="D16" t="s">
         <v>6</v>
       </c>
+      <c r="E16" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="17" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A17" s="22">
@@ -1187,6 +1231,9 @@
       <c r="D17" t="s">
         <v>6</v>
       </c>
+      <c r="E17" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="18" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A18" s="22">
@@ -1202,6 +1249,9 @@
       <c r="D18" t="s">
         <v>6</v>
       </c>
+      <c r="E18" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A19" s="22">
@@ -1217,6 +1267,9 @@
       <c r="D19" t="s">
         <v>6</v>
       </c>
+      <c r="E19" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A20" s="22">
@@ -1232,6 +1285,9 @@
       <c r="D20" t="s">
         <v>6</v>
       </c>
+      <c r="E20" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A21" s="22">
@@ -1242,9 +1298,12 @@
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1257,9 +1316,12 @@
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D22" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1272,9 +1334,12 @@
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1292,6 +1357,9 @@
       <c r="D24" t="s">
         <v>6</v>
       </c>
+      <c r="E24" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="25" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A25" s="22">
@@ -1302,9 +1370,12 @@
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1322,6 +1393,9 @@
       <c r="D26" t="s">
         <v>6</v>
       </c>
+      <c r="E26" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="27" spans="1:35" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="22">
@@ -1335,6 +1409,9 @@
         <v>100</v>
       </c>
       <c r="D27" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" t="s">
         <v>6</v>
       </c>
       <c r="M27"/>
@@ -1375,6 +1452,9 @@
       <c r="D28" t="s">
         <v>6</v>
       </c>
+      <c r="E28" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="29" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A29" s="20">
@@ -1390,6 +1470,9 @@
       <c r="D29" t="s">
         <v>4</v>
       </c>
+      <c r="E29" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="30" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A30" s="22">
@@ -1400,9 +1483,12 @@
       </c>
       <c r="C30">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D30" t="s">
+        <v>4</v>
+      </c>
+      <c r="E30" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1415,9 +1501,12 @@
       </c>
       <c r="C31">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D31" t="s">
+        <v>4</v>
+      </c>
+      <c r="E31" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1430,13 +1519,16 @@
       </c>
       <c r="C32">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D32" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E32" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="22">
         <v>2452020924</v>
       </c>
@@ -1445,13 +1537,16 @@
       </c>
       <c r="C33">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E33" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="22">
         <v>2452020927</v>
       </c>
@@ -1460,13 +1555,16 @@
       </c>
       <c r="C34">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D34" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="22">
         <v>2452020928</v>
       </c>
@@ -1480,8 +1578,11 @@
       <c r="D35" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="22">
         <v>2452020931</v>
       </c>
@@ -1495,8 +1596,11 @@
       <c r="D36" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="22">
         <v>2452020932</v>
       </c>
@@ -1510,8 +1614,11 @@
       <c r="D37" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="22">
         <v>2452020934</v>
       </c>
@@ -1520,13 +1627,16 @@
       </c>
       <c r="C38">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D38" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E38" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="22">
         <v>2452020935</v>
       </c>
@@ -1540,8 +1650,11 @@
       <c r="D39" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="22">
         <v>2452020937</v>
       </c>
@@ -1555,8 +1668,11 @@
       <c r="D40" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="22">
         <v>2452020939</v>
       </c>
@@ -1565,13 +1681,16 @@
       </c>
       <c r="C41">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D41" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E41" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="20">
         <v>2452020940</v>
       </c>
@@ -1585,8 +1704,11 @@
       <c r="D42" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="22">
         <v>2452020941</v>
       </c>
@@ -1600,8 +1722,11 @@
       <c r="D43" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="22">
         <v>2452020942</v>
       </c>
@@ -1610,13 +1735,16 @@
       </c>
       <c r="C44">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D44" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E44" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="22">
         <v>2452020945</v>
       </c>
@@ -1630,8 +1758,11 @@
       <c r="D45" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E45" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="22">
         <v>2452020949</v>
       </c>
@@ -1645,8 +1776,11 @@
       <c r="D46" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="22">
         <v>2452020950</v>
       </c>
@@ -1660,8 +1794,11 @@
       <c r="D47" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E47" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="22">
         <v>2452020953</v>
       </c>
@@ -1670,13 +1807,16 @@
       </c>
       <c r="C48">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D48" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E48" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="22">
         <v>2452020955</v>
       </c>
@@ -1690,8 +1830,11 @@
       <c r="D49" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E49" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="22">
         <v>2452020958</v>
       </c>
@@ -1700,13 +1843,16 @@
       </c>
       <c r="C50">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D50" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E50" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="22">
         <v>2452020963</v>
       </c>
@@ -1715,13 +1861,16 @@
       </c>
       <c r="C51">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D51" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E51" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="22">
         <v>2452020966</v>
       </c>
@@ -1730,13 +1879,16 @@
       </c>
       <c r="C52">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D52" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E52" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="23">
         <v>2452020968</v>
       </c>
@@ -1745,13 +1897,16 @@
       </c>
       <c r="C53">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D53" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E53" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="22">
         <v>2452020970</v>
       </c>
@@ -1760,13 +1915,16 @@
       </c>
       <c r="C54">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D54" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E54" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="20">
         <v>2452020972</v>
       </c>
@@ -1775,13 +1933,16 @@
       </c>
       <c r="C55">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D55" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E55" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="22">
         <v>2452020974</v>
       </c>
@@ -1795,8 +1956,11 @@
       <c r="D56" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E56" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="22">
         <v>2452020977</v>
       </c>
@@ -1805,13 +1969,16 @@
       </c>
       <c r="C57">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D57" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E57" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="22">
         <v>2452020981</v>
       </c>
@@ -1825,8 +1992,11 @@
       <c r="D58" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E58" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="22">
         <v>2452020983</v>
       </c>
@@ -1840,8 +2010,11 @@
       <c r="D59" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E59" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="22">
         <v>2452021017</v>
       </c>
@@ -1855,8 +2028,11 @@
       <c r="D60" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E60" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="22">
         <v>2452021026</v>
       </c>
@@ -1870,8 +2046,11 @@
       <c r="D61" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E61" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="22">
         <v>2452021389</v>
       </c>
@@ -1880,13 +2059,16 @@
       </c>
       <c r="C62">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D62" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E62" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="22">
         <v>2452021400</v>
       </c>
@@ -1895,267 +2077,270 @@
       </c>
       <c r="C63">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D63" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E63" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="10"/>
       <c r="B64" s="10"/>
     </row>
-    <row r="65" spans="3:64" ht="78" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C65" s="33">
+    <row r="65" spans="4:65" ht="78" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D65">
         <f>COUNTIF(D3:D49,"×")</f>
         <v>17</v>
       </c>
-      <c r="D65" s="33">
-        <f t="shared" ref="D65:BJ65" si="1">COUNTIF(E3:E49,"×")</f>
-        <v>0</v>
-      </c>
-      <c r="E65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AB65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AC65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AD65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AE65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AF65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AG65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AH65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AI65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AJ65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AK65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AL65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AM65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AN65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AO65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AP65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AQ65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AR65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AS65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AT65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AU65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AV65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AW65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AX65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AY65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AZ65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BA65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BB65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BC65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BD65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BE65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BF65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BG65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BH65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BI65" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BJ65" s="33">
+      <c r="E65">
+        <f t="shared" ref="E65:BM65" si="1">COUNTIF(E3:E49,"×")</f>
+        <v>23</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BB65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BC65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BD65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BE65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BF65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BG65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BH65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BI65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BJ65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="BK65">
-        <f t="shared" ref="AJ65:BL65" si="2">COUNTIF(BK3:BK64,"×")</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="BL65">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="3:64" ht="30" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BM65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="4:65" ht="30" x14ac:dyDescent="0.4">
       <c r="H67" s="27" t="s">
         <v>66</v>
       </c>
@@ -2175,7 +2360,7 @@
     <mergeCell ref="C1:C2"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
-  <conditionalFormatting sqref="C64:C1048576 C1:C2 D65:BJ65">
+  <conditionalFormatting sqref="C64:C1048576 C1:C2">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="percentile" val="20"/>

--- a/24网络技术4班考勤.xlsx
+++ b/24网络技术4班考勤.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\2026\教学\4班\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="考勤" sheetId="3" r:id="rId1"/>
@@ -17,12 +12,12 @@
     <sheet name="实验报告" sheetId="5" r:id="rId3"/>
     <sheet name="打扫卫生" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="114">
   <si>
     <t>学号</t>
   </si>
@@ -369,8 +364,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="15" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -389,37 +390,37 @@
       <sz val="9"/>
       <color theme="9"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF00B050"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <color theme="6" tint="0.39963988158818325"/>
+      <color theme="6" tint="0.399639881588183"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -436,7 +437,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="6" tint="0.39963988158818325"/>
+      <color theme="6" tint="0.399639881588183"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -445,7 +446,7 @@
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -461,14 +462,151 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -493,8 +631,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -574,13 +898,257 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -617,7 +1185,13 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -629,6 +1203,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -647,29 +1224,62 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -927,53 +1537,56 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:BM67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="29" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="31"/>
+    <row r="2" ht="15" spans="1:34">
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="24"/>
       <c r="D2">
         <v>3.06</v>
       </c>
       <c r="E2">
         <v>3.07</v>
       </c>
-      <c r="O2" s="25"/>
-      <c r="AF2" s="26"/>
-      <c r="AH2" s="26"/>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A3" s="20">
+      <c r="F2">
+        <v>3.09</v>
+      </c>
+      <c r="O2" s="30"/>
+      <c r="AF2" s="31"/>
+      <c r="AH2" s="31"/>
+    </row>
+    <row r="3" ht="15.75" spans="1:6">
+      <c r="A3" s="25">
         <v>2452020847</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="26" t="s">
         <v>3</v>
       </c>
       <c r="C3">
         <f>100-COUNTIF(D3:AZ3,"×")*3</f>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
@@ -981,12 +1594,15 @@
       <c r="E3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A4" s="22">
+      <c r="F3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" ht="15" spans="1:6">
+      <c r="A4" s="27">
         <v>2452020850</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="26" t="s">
         <v>5</v>
       </c>
       <c r="C4">
@@ -999,12 +1615,15 @@
       <c r="E4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A5" s="22">
+      <c r="F4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" ht="15" spans="1:6">
+      <c r="A5" s="27">
         <v>2452020851</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="26" t="s">
         <v>7</v>
       </c>
       <c r="C5">
@@ -1017,12 +1636,15 @@
       <c r="E5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A6" s="22">
+      <c r="F5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="1:25">
+      <c r="A6" s="27">
         <v>2452020852</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="26" t="s">
         <v>8</v>
       </c>
       <c r="C6">
@@ -1035,13 +1657,16 @@
       <c r="E6" t="s">
         <v>4</v>
       </c>
-      <c r="Y6" s="26"/>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A7" s="22">
+      <c r="F6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y6" s="31"/>
+    </row>
+    <row r="7" ht="15" spans="1:6">
+      <c r="A7" s="27">
         <v>2452020854</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="26" t="s">
         <v>9</v>
       </c>
       <c r="C7">
@@ -1054,17 +1679,20 @@
       <c r="E7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A8" s="22">
+      <c r="F7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="15" spans="1:6">
+      <c r="A8" s="27">
         <v>2452020855</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="26" t="s">
         <v>10</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
         <v>4</v>
@@ -1072,12 +1700,15 @@
       <c r="E8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A9" s="22">
+      <c r="F8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" ht="15" spans="1:6">
+      <c r="A9" s="27">
         <v>2452020858</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="26" t="s">
         <v>11</v>
       </c>
       <c r="C9">
@@ -1090,17 +1721,20 @@
       <c r="E9" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A10" s="22">
+      <c r="F9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="1:6">
+      <c r="A10" s="27">
         <v>2452020859</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="26" t="s">
         <v>12</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
         <v>4</v>
@@ -1108,12 +1742,15 @@
       <c r="E10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A11" s="22">
+      <c r="F10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" ht="15" spans="1:6">
+      <c r="A11" s="27">
         <v>2452020863</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="26" t="s">
         <v>13</v>
       </c>
       <c r="C11">
@@ -1126,17 +1763,20 @@
       <c r="E11" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A12" s="22">
+      <c r="F11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="1:6">
+      <c r="A12" s="27">
         <v>2452020864</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="26" t="s">
         <v>14</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
         <v>4</v>
@@ -1144,17 +1784,20 @@
       <c r="E12" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A13" s="22">
+      <c r="F12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" ht="15" spans="1:6">
+      <c r="A13" s="27">
         <v>2452020865</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="26" t="s">
         <v>15</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
         <v>6</v>
@@ -1162,17 +1805,20 @@
       <c r="E13" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A14" s="22">
+      <c r="F13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" ht="15" spans="1:6">
+      <c r="A14" s="27">
         <v>2452020867</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="26" t="s">
         <v>16</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
         <v>4</v>
@@ -1180,12 +1826,15 @@
       <c r="E14" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A15" s="22">
+      <c r="F14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" ht="15" spans="1:6">
+      <c r="A15" s="27">
         <v>2452020869</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="26" t="s">
         <v>17</v>
       </c>
       <c r="C15">
@@ -1198,12 +1847,15 @@
       <c r="E15" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A16" s="20">
+      <c r="F15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="1:6">
+      <c r="A16" s="25">
         <v>2452020870</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="26" t="s">
         <v>18</v>
       </c>
       <c r="C16">
@@ -1216,12 +1868,15 @@
       <c r="E16" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A17" s="22">
+      <c r="F16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" ht="15" spans="1:6">
+      <c r="A17" s="27">
         <v>2452020873</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="26" t="s">
         <v>19</v>
       </c>
       <c r="C17">
@@ -1234,12 +1889,15 @@
       <c r="E17" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A18" s="22">
+      <c r="F17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="27">
         <v>2452020877</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="26" t="s">
         <v>20</v>
       </c>
       <c r="C18">
@@ -1252,12 +1910,15 @@
       <c r="E18" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A19" s="22">
+      <c r="F18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" ht="15" spans="1:6">
+      <c r="A19" s="27">
         <v>2452020878</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="26" t="s">
         <v>21</v>
       </c>
       <c r="C19">
@@ -1270,12 +1931,15 @@
       <c r="E19" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A20" s="22">
+      <c r="F19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" ht="15" spans="1:6">
+      <c r="A20" s="27">
         <v>2452020879</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="26" t="s">
         <v>22</v>
       </c>
       <c r="C20">
@@ -1288,17 +1952,20 @@
       <c r="E20" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A21" s="22">
+      <c r="F20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" ht="15" spans="1:6">
+      <c r="A21" s="27">
         <v>2452020881</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="26" t="s">
         <v>23</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D21" t="s">
         <v>4</v>
@@ -1306,17 +1973,20 @@
       <c r="E21" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A22" s="22">
+      <c r="F21" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" ht="15" spans="1:6">
+      <c r="A22" s="27">
         <v>2452020882</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D22" t="s">
         <v>4</v>
@@ -1324,17 +1994,20 @@
       <c r="E22" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A23" s="22">
+      <c r="F22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" ht="15" spans="1:6">
+      <c r="A23" s="27">
         <v>2452020889</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="26" t="s">
         <v>25</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D23" t="s">
         <v>4</v>
@@ -1342,17 +2015,20 @@
       <c r="E23" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A24" s="22">
+      <c r="F23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" ht="15" spans="1:6">
+      <c r="A24" s="27">
         <v>2452020899</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="26" t="s">
         <v>26</v>
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s">
         <v>6</v>
@@ -1360,17 +2036,20 @@
       <c r="E24" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A25" s="22">
+      <c r="F24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" ht="15" spans="1:6">
+      <c r="A25" s="27">
         <v>2452020906</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="26" t="s">
         <v>27</v>
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D25" t="s">
         <v>4</v>
@@ -1378,12 +2057,15 @@
       <c r="E25" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A26" s="22">
+      <c r="F25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" ht="15" spans="1:6">
+      <c r="A26" s="27">
         <v>2452020909</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="26" t="s">
         <v>28</v>
       </c>
       <c r="C26">
@@ -1396,12 +2078,15 @@
       <c r="E26" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="27" spans="1:35" s="19" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="22">
+      <c r="F26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" s="23" customFormat="1" ht="15" spans="1:35">
+      <c r="A27" s="27">
         <v>2452020910</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="26" t="s">
         <v>29</v>
       </c>
       <c r="C27">
@@ -1412,6 +2097,9 @@
         <v>6</v>
       </c>
       <c r="E27" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27" t="s">
         <v>6</v>
       </c>
       <c r="M27"/>
@@ -1438,11 +2126,11 @@
       <c r="AH27"/>
       <c r="AI27"/>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A28" s="20">
+    <row r="28" ht="15" spans="1:6">
+      <c r="A28" s="25">
         <v>2452020911</v>
       </c>
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C28">
@@ -1455,12 +2143,15 @@
       <c r="E28" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A29" s="20">
+      <c r="F28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" ht="15" spans="1:6">
+      <c r="A29" s="25">
         <v>2452020917</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="26" t="s">
         <v>31</v>
       </c>
       <c r="C29">
@@ -1473,12 +2164,15 @@
       <c r="E29" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A30" s="22">
+      <c r="F29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" ht="15" spans="1:6">
+      <c r="A30" s="27">
         <v>2452020919</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="26" t="s">
         <v>32</v>
       </c>
       <c r="C30">
@@ -1491,233 +2185,272 @@
       <c r="E30" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A31" s="22">
+      <c r="F30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" ht="15" spans="1:6">
+      <c r="A31" s="27">
         <v>2452020920</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="26" t="s">
         <v>33</v>
       </c>
       <c r="C31">
         <f t="shared" si="0"/>
+        <v>91</v>
+      </c>
+      <c r="D31" t="s">
+        <v>4</v>
+      </c>
+      <c r="E31" t="s">
+        <v>4</v>
+      </c>
+      <c r="F31" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" ht="15" spans="1:6">
+      <c r="A32" s="27">
+        <v>2452020922</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="0"/>
         <v>94</v>
       </c>
-      <c r="D31" t="s">
-        <v>4</v>
-      </c>
-      <c r="E31" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A32" s="22">
-        <v>2452020922</v>
-      </c>
-      <c r="B32" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32">
+      <c r="D32" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" ht="15" spans="1:6">
+      <c r="A33" s="27">
+        <v>2452020924</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
-      <c r="D32" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="22">
-        <v>2452020924</v>
-      </c>
-      <c r="B33" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33">
+      <c r="D33" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" ht="15" spans="1:6">
+      <c r="A34" s="27">
+        <v>2452020927</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="0"/>
+        <v>91</v>
+      </c>
+      <c r="D34" t="s">
+        <v>4</v>
+      </c>
+      <c r="E34" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" ht="15" spans="1:6">
+      <c r="A35" s="27">
+        <v>2452020928</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D35" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35" t="s">
+        <v>6</v>
+      </c>
+      <c r="F35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="27">
+        <v>2452020931</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D36" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36" t="s">
+        <v>6</v>
+      </c>
+      <c r="F36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" ht="15" spans="1:6">
+      <c r="A37" s="27">
+        <v>2452020932</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D37" t="s">
+        <v>6</v>
+      </c>
+      <c r="E37" t="s">
+        <v>6</v>
+      </c>
+      <c r="F37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" ht="15" spans="1:6">
+      <c r="A38" s="27">
+        <v>2452020934</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="0"/>
+        <v>94</v>
+      </c>
+      <c r="D38" t="s">
+        <v>6</v>
+      </c>
+      <c r="E38" t="s">
+        <v>4</v>
+      </c>
+      <c r="F38" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" ht="15" spans="1:6">
+      <c r="A39" s="27">
+        <v>2452020935</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D39" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" t="s">
+        <v>6</v>
+      </c>
+      <c r="F39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" ht="15" spans="1:6">
+      <c r="A40" s="27">
+        <v>2452020937</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C40">
         <f t="shared" si="0"/>
         <v>97</v>
       </c>
-      <c r="D33" t="s">
-        <v>6</v>
-      </c>
-      <c r="E33" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="22">
-        <v>2452020927</v>
-      </c>
-      <c r="B34" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C34">
-        <f t="shared" si="0"/>
-        <v>94</v>
-      </c>
-      <c r="D34" t="s">
-        <v>4</v>
-      </c>
-      <c r="E34" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="22">
-        <v>2452020928</v>
-      </c>
-      <c r="B35" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C35">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D35" t="s">
-        <v>6</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="22">
-        <v>2452020931</v>
-      </c>
-      <c r="B36" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D36" t="s">
-        <v>6</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="22">
-        <v>2452020932</v>
-      </c>
-      <c r="B37" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C37">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D37" t="s">
-        <v>6</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="22">
-        <v>2452020934</v>
-      </c>
-      <c r="B38" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C38">
+      <c r="D40" t="s">
+        <v>6</v>
+      </c>
+      <c r="E40" t="s">
+        <v>6</v>
+      </c>
+      <c r="F40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" ht="15" spans="1:6">
+      <c r="A41" s="27">
+        <v>2452020939</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="0"/>
+        <v>91</v>
+      </c>
+      <c r="D41" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" t="s">
+        <v>4</v>
+      </c>
+      <c r="F41" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" ht="15" spans="1:6">
+      <c r="A42" s="25">
+        <v>2452020940</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42">
         <f t="shared" si="0"/>
         <v>97</v>
       </c>
-      <c r="D38" t="s">
-        <v>6</v>
-      </c>
-      <c r="E38" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" s="22">
-        <v>2452020935</v>
-      </c>
-      <c r="B39" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D39" t="s">
-        <v>6</v>
-      </c>
-      <c r="E39" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" s="22">
-        <v>2452020937</v>
-      </c>
-      <c r="B40" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="C40">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D40" t="s">
-        <v>6</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" s="22">
-        <v>2452020939</v>
-      </c>
-      <c r="B41" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C41">
-        <f t="shared" si="0"/>
-        <v>94</v>
-      </c>
-      <c r="D41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E41" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" s="20">
-        <v>2452020940</v>
-      </c>
-      <c r="B42" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="C42">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
       <c r="D42" t="s">
         <v>6</v>
       </c>
       <c r="E42" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="22">
+      <c r="F42" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" ht="15" spans="1:6">
+      <c r="A43" s="27">
         <v>2452020941</v>
       </c>
-      <c r="B43" s="21" t="s">
+      <c r="B43" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C43">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D43" t="s">
         <v>6</v>
@@ -1725,17 +2458,20 @@
       <c r="E43" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" s="22">
+      <c r="F43" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" ht="15" spans="1:6">
+      <c r="A44" s="27">
         <v>2452020942</v>
       </c>
-      <c r="B44" s="21" t="s">
+      <c r="B44" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C44">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D44" t="s">
         <v>4</v>
@@ -1743,12 +2479,15 @@
       <c r="E44" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="22">
+      <c r="F44" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" ht="15" spans="1:6">
+      <c r="A45" s="27">
         <v>2452020945</v>
       </c>
-      <c r="B45" s="21" t="s">
+      <c r="B45" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C45">
@@ -1761,12 +2500,15 @@
       <c r="E45" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" s="22">
+      <c r="F45" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" ht="15" spans="1:6">
+      <c r="A46" s="27">
         <v>2452020949</v>
       </c>
-      <c r="B46" s="21" t="s">
+      <c r="B46" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C46">
@@ -1779,17 +2521,20 @@
       <c r="E46" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="22">
+      <c r="F46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" ht="15" spans="1:6">
+      <c r="A47" s="27">
         <v>2452020950</v>
       </c>
-      <c r="B47" s="21" t="s">
+      <c r="B47" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C47">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D47" t="s">
         <v>6</v>
@@ -1797,71 +2542,83 @@
       <c r="E47" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="22">
+      <c r="F47" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" ht="15" spans="1:6">
+      <c r="A48" s="27">
         <v>2452020953</v>
       </c>
-      <c r="B48" s="21" t="s">
+      <c r="B48" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C48">
         <f t="shared" si="0"/>
+        <v>91</v>
+      </c>
+      <c r="D48" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" ht="15" spans="1:6">
+      <c r="A49" s="27">
+        <v>2452020955</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D49" t="s">
+        <v>6</v>
+      </c>
+      <c r="E49" t="s">
+        <v>6</v>
+      </c>
+      <c r="F49" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" ht="15" spans="1:6">
+      <c r="A50" s="27">
+        <v>2452020958</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C50">
+        <f t="shared" si="0"/>
         <v>94</v>
       </c>
-      <c r="D48" t="s">
-        <v>4</v>
-      </c>
-      <c r="E48" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" s="22">
-        <v>2452020955</v>
-      </c>
-      <c r="B49" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="C49">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D49" t="s">
-        <v>6</v>
-      </c>
-      <c r="E49" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" s="22">
-        <v>2452020958</v>
-      </c>
-      <c r="B50" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="C50">
-        <f t="shared" si="0"/>
-        <v>94</v>
-      </c>
       <c r="D50" t="s">
         <v>4</v>
       </c>
       <c r="E50" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" s="22">
+      <c r="F50" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" ht="15" spans="1:6">
+      <c r="A51" s="27">
         <v>2452020963</v>
       </c>
-      <c r="B51" s="21" t="s">
+      <c r="B51" s="26" t="s">
         <v>53</v>
       </c>
       <c r="C51">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D51" t="s">
         <v>4</v>
@@ -1869,17 +2626,20 @@
       <c r="E51" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" s="22">
+      <c r="F51" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" ht="15" spans="1:6">
+      <c r="A52" s="27">
         <v>2452020966</v>
       </c>
-      <c r="B52" s="21" t="s">
+      <c r="B52" s="26" t="s">
         <v>54</v>
       </c>
       <c r="C52">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D52" t="s">
         <v>4</v>
@@ -1887,17 +2647,20 @@
       <c r="E52" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" s="23">
+      <c r="F52" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" ht="15" spans="1:6">
+      <c r="A53" s="28">
         <v>2452020968</v>
       </c>
-      <c r="B53" s="24" t="s">
+      <c r="B53" s="29" t="s">
         <v>55</v>
       </c>
       <c r="C53">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D53" t="s">
         <v>4</v>
@@ -1905,17 +2668,20 @@
       <c r="E53" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" s="22">
+      <c r="F53" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" ht="15" spans="1:6">
+      <c r="A54" s="27">
         <v>2452020970</v>
       </c>
-      <c r="B54" s="21" t="s">
+      <c r="B54" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C54">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D54" t="s">
         <v>4</v>
@@ -1923,17 +2689,20 @@
       <c r="E54" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" s="20">
+      <c r="F54" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" ht="15" spans="1:6">
+      <c r="A55" s="25">
         <v>2452020972</v>
       </c>
-      <c r="B55" s="21" t="s">
+      <c r="B55" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C55">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D55" t="s">
         <v>4</v>
@@ -1941,17 +2710,20 @@
       <c r="E55" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" s="22">
+      <c r="F55" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" ht="15" spans="1:6">
+      <c r="A56" s="27">
         <v>2452020974</v>
       </c>
-      <c r="B56" s="21" t="s">
+      <c r="B56" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C56">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D56" t="s">
         <v>6</v>
@@ -1959,17 +2731,20 @@
       <c r="E56" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" s="22">
+      <c r="F56" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" ht="15" spans="1:6">
+      <c r="A57" s="27">
         <v>2452020977</v>
       </c>
-      <c r="B57" s="21" t="s">
+      <c r="B57" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C57">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D57" t="s">
         <v>4</v>
@@ -1977,12 +2752,15 @@
       <c r="E57" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58" s="22">
+      <c r="F57" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" ht="15" spans="1:6">
+      <c r="A58" s="27">
         <v>2452020981</v>
       </c>
-      <c r="B58" s="21" t="s">
+      <c r="B58" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C58">
@@ -1995,17 +2773,20 @@
       <c r="E58" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" s="22">
+      <c r="F58" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" ht="15" spans="1:6">
+      <c r="A59" s="27">
         <v>2452020983</v>
       </c>
-      <c r="B59" s="21" t="s">
+      <c r="B59" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C59">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D59" t="s">
         <v>6</v>
@@ -2013,17 +2794,20 @@
       <c r="E59" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" s="22">
+      <c r="F59" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" ht="15" spans="1:6">
+      <c r="A60" s="27">
         <v>2452021017</v>
       </c>
-      <c r="B60" s="21" t="s">
+      <c r="B60" s="26" t="s">
         <v>62</v>
       </c>
       <c r="C60">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D60" t="s">
         <v>6</v>
@@ -2031,17 +2815,20 @@
       <c r="E60" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61" s="22">
+      <c r="F60" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" ht="15" spans="1:6">
+      <c r="A61" s="27">
         <v>2452021026</v>
       </c>
-      <c r="B61" s="21" t="s">
+      <c r="B61" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C61">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D61" t="s">
         <v>6</v>
@@ -2049,17 +2836,20 @@
       <c r="E61" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" s="22">
+      <c r="F61" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" ht="15" spans="1:6">
+      <c r="A62" s="27">
         <v>2452021389</v>
       </c>
-      <c r="B62" s="21" t="s">
+      <c r="B62" s="26" t="s">
         <v>64</v>
       </c>
       <c r="C62">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D62" t="s">
         <v>4</v>
@@ -2067,17 +2857,20 @@
       <c r="E62" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A63" s="22">
+      <c r="F62" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" ht="15" spans="1:6">
+      <c r="A63" s="27">
         <v>2452021400</v>
       </c>
-      <c r="B63" s="21" t="s">
+      <c r="B63" s="26" t="s">
         <v>65</v>
       </c>
       <c r="C63">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D63" t="s">
         <v>4</v>
@@ -2085,12 +2878,15 @@
       <c r="E63" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A64" s="10"/>
-      <c r="B64" s="10"/>
-    </row>
-    <row r="65" spans="4:65" ht="78" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F63" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" ht="15" spans="1:2">
+      <c r="A64" s="12"/>
+      <c r="B64" s="12"/>
+    </row>
+    <row r="65" ht="78" customHeight="1" spans="4:65">
       <c r="D65">
         <f>COUNTIF(D3:D49,"×")</f>
         <v>17</v>
@@ -2101,7 +2897,7 @@
       </c>
       <c r="F65">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G65">
         <f t="shared" si="1"/>
@@ -2340,17 +3136,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="4:65" ht="30" x14ac:dyDescent="0.4">
-      <c r="H67" s="27" t="s">
+    <row r="67" ht="30" spans="8:15">
+      <c r="H67" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="I67" s="28"/>
-      <c r="J67" s="28"/>
-      <c r="K67" s="28"/>
-      <c r="L67" s="28"/>
-      <c r="M67" s="28"/>
-      <c r="N67" s="28"/>
-      <c r="O67" s="28"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3"/>
+      <c r="K67" s="3"/>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2359,7 +3155,6 @@
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
   </mergeCells>
-  <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="C64:C1048576 C1:C2">
     <cfRule type="colorScale" priority="7">
       <colorScale>
@@ -2382,545 +3177,548 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
-  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="15.625" customWidth="1"/>
     <col min="4" max="5" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="14"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="30"/>
-      <c r="B2" s="15" t="s">
+      <c r="B1" s="17"/>
+    </row>
+    <row r="2" ht="15" spans="1:5">
+      <c r="A2" s="18"/>
+      <c r="B2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-    </row>
-    <row r="3" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A3" s="10" t="s">
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" ht="24.75" spans="1:4">
+      <c r="A3" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="17">
+      <c r="B3" s="21">
         <f>100-COUNTIF(C3:AZ3,"△")*30</f>
         <v>100</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-    </row>
-    <row r="4" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+    </row>
+    <row r="4" ht="24" spans="1:4">
+      <c r="A4" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="21">
         <f t="shared" ref="B4:B49" si="0">100-COUNTIF(C4:AZ4,"△")*30</f>
         <v>100</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-    </row>
-    <row r="5" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A5" s="10" t="s">
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+    </row>
+    <row r="5" ht="24" spans="1:5">
+      <c r="A5" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
+      <c r="B5" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+    </row>
+    <row r="6" ht="24" spans="1:4">
+      <c r="A6" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
+      <c r="B6" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+    </row>
+    <row r="7" ht="15" spans="1:2">
+      <c r="A7" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="9" t="s">
+      <c r="B7" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" ht="15" spans="1:2">
+      <c r="A8" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A9" s="10" t="s">
+      <c r="B8" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" ht="24" spans="1:4">
+      <c r="A9" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D9" s="18"/>
-    </row>
-    <row r="10" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
+      <c r="B9" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D9" s="22"/>
+    </row>
+    <row r="10" ht="24" spans="1:4">
+      <c r="A10" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="B10" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-    </row>
-    <row r="11" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A11" s="12" t="s">
+      <c r="B10" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+    </row>
+    <row r="11" ht="24" spans="1:5">
+      <c r="A11" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-    </row>
-    <row r="12" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
+      <c r="B11" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+    </row>
+    <row r="12" ht="24" spans="1:4">
+      <c r="A12" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D12" s="18"/>
-    </row>
-    <row r="13" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A13" s="10" t="s">
+      <c r="B12" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D12" s="22"/>
+    </row>
+    <row r="13" ht="24" spans="1:4">
+      <c r="A13" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B13" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D13" s="18"/>
-    </row>
-    <row r="14" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
+      <c r="B13" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D13" s="22"/>
+    </row>
+    <row r="14" ht="24" spans="1:4">
+      <c r="A14" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D14" s="18"/>
-    </row>
-    <row r="15" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A15" s="10" t="s">
+      <c r="B14" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D14" s="22"/>
+    </row>
+    <row r="15" ht="24" spans="1:4">
+      <c r="A15" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="B15" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D15" s="18"/>
-    </row>
-    <row r="16" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A16" s="9" t="s">
+      <c r="B15" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D15" s="22"/>
+    </row>
+    <row r="16" ht="24" spans="1:5">
+      <c r="A16" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="B16" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-    </row>
-    <row r="17" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
+      <c r="B16" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+    </row>
+    <row r="17" ht="24" spans="1:4">
+      <c r="A17" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B17" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D17" s="18"/>
-    </row>
-    <row r="18" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A18" s="9" t="s">
+      <c r="B17" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D17" s="22"/>
+    </row>
+    <row r="18" ht="24" spans="1:4">
+      <c r="A18" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D18" s="18"/>
-    </row>
-    <row r="19" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A19" s="10" t="s">
+      <c r="B18" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D18" s="22"/>
+    </row>
+    <row r="19" ht="24" spans="1:5">
+      <c r="A19" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-    </row>
-    <row r="20" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A20" s="9" t="s">
+      <c r="B19" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+    </row>
+    <row r="20" ht="24" spans="1:4">
+      <c r="A20" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="B20" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D20" s="18"/>
-    </row>
-    <row r="21" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A21" s="10" t="s">
+      <c r="B20" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D20" s="22"/>
+    </row>
+    <row r="21" ht="24" spans="1:4">
+      <c r="A21" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D21" s="18"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="9" t="s">
+      <c r="B21" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D21" s="22"/>
+    </row>
+    <row r="22" ht="15" spans="1:2">
+      <c r="A22" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="B22" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="10" t="s">
+      <c r="B22" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" ht="15" spans="1:2">
+      <c r="A23" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="B23" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A24" s="9" t="s">
+      <c r="B23" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" ht="24" spans="1:5">
+      <c r="A24" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B24" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-    </row>
-    <row r="25" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A25" s="10" t="s">
+      <c r="B24" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+    </row>
+    <row r="25" ht="24" spans="1:5">
+      <c r="A25" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="B25" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-    </row>
-    <row r="26" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A26" s="9" t="s">
+      <c r="B25" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+    </row>
+    <row r="26" ht="24" spans="1:5">
+      <c r="A26" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B26" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-    </row>
-    <row r="27" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A27" s="13" t="s">
+      <c r="B26" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+    </row>
+    <row r="27" ht="24" spans="1:5">
+      <c r="A27" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="B27" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="9" t="s">
+      <c r="B27" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+    </row>
+    <row r="28" ht="15" spans="1:2">
+      <c r="A28" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B28" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="10" t="s">
+      <c r="B28" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" ht="15" spans="1:2">
+      <c r="A29" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="B29" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A30" s="9" t="s">
+      <c r="B29" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" ht="24" spans="1:5">
+      <c r="A30" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="B30" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-    </row>
-    <row r="31" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A31" s="10" t="s">
+      <c r="B30" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+    </row>
+    <row r="31" ht="24" spans="1:5">
+      <c r="A31" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B31" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-    </row>
-    <row r="32" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A32" s="9" t="s">
+      <c r="B31" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+    </row>
+    <row r="32" ht="24" spans="1:4">
+      <c r="A32" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="B32" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-    </row>
-    <row r="33" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A33" s="10" t="s">
+      <c r="B32" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+    </row>
+    <row r="33" ht="24" spans="1:3">
+      <c r="A33" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="B33" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C33" s="18"/>
-    </row>
-    <row r="34" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A34" s="9" t="s">
+      <c r="B33" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C33" s="22"/>
+    </row>
+    <row r="34" ht="24" spans="1:5">
+      <c r="A34" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B34" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-    </row>
-    <row r="35" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A35" s="10" t="s">
+      <c r="B34" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+    </row>
+    <row r="35" ht="24" spans="1:5">
+      <c r="A35" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="B35" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="B36" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A37" s="10" t="s">
+      <c r="B35" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+    </row>
+    <row r="36" ht="15" spans="1:2">
+      <c r="A36" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" ht="24" spans="1:5">
+      <c r="A37" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="B37" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-    </row>
-    <row r="38" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A38" s="9" t="s">
+      <c r="B37" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+    </row>
+    <row r="38" ht="24" spans="1:5">
+      <c r="A38" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="B38" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-    </row>
-    <row r="39" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A39" s="10" t="s">
+      <c r="B38" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+    </row>
+    <row r="39" ht="24" spans="1:5">
+      <c r="A39" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="B39" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-    </row>
-    <row r="40" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A40" s="9" t="s">
+      <c r="B39" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+    </row>
+    <row r="40" ht="24" spans="1:5">
+      <c r="A40" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B40" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-    </row>
-    <row r="41" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A41" s="10" t="s">
+      <c r="B40" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+    </row>
+    <row r="41" ht="24" spans="1:4">
+      <c r="A41" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B41" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D41" s="18"/>
-    </row>
-    <row r="42" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A42" s="9" t="s">
+      <c r="B41" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D41" s="22"/>
+    </row>
+    <row r="42" ht="24" spans="1:5">
+      <c r="A42" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="B42" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="10" t="s">
+      <c r="B42" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+    </row>
+    <row r="43" ht="15" spans="1:2">
+      <c r="A43" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="B43" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A44" s="9" t="s">
+      <c r="B43" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" ht="24" spans="1:5">
+      <c r="A44" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="B44" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-    </row>
-    <row r="45" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A45" s="10" t="s">
+      <c r="B44" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+    </row>
+    <row r="45" ht="24" spans="1:5">
+      <c r="A45" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="B45" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-    </row>
-    <row r="46" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A46" s="9" t="s">
+      <c r="B45" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+    </row>
+    <row r="46" ht="24" spans="1:5">
+      <c r="A46" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="B46" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
-      <c r="E46" s="18"/>
-    </row>
-    <row r="47" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A47" s="10" t="s">
+      <c r="B46" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C46" s="22"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+    </row>
+    <row r="47" ht="24" spans="1:5">
+      <c r="A47" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B47" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="9" t="s">
+      <c r="B47" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+    </row>
+    <row r="48" ht="15" spans="1:2">
+      <c r="A48" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B48" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" s="10" t="s">
+      <c r="B48" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" ht="15" spans="1:2">
+      <c r="A49" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B49" s="17">
+      <c r="B49" s="21">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
@@ -2929,203 +3727,205 @@
   <mergeCells count="1">
     <mergeCell ref="A1:A2"/>
   </mergeCells>
-  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" s="32"/>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-    </row>
-    <row r="3" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="5"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="5"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="8"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="7"/>
-      <c r="M7" s="10"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="7"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="10"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="4"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="8"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="H9" s="11"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="4"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="3"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="2"/>
-      <c r="H10" s="12"/>
-      <c r="K10" s="4"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
-      <c r="D11" s="4"/>
-      <c r="H11" s="9"/>
-      <c r="K11" s="7"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="3"/>
-      <c r="D12" s="13"/>
-      <c r="K12" s="4"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="8"/>
-      <c r="D13" s="3"/>
-      <c r="K13" s="10"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="D14" s="2"/>
-      <c r="K14" s="4"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="D15" s="4"/>
-      <c r="K15" s="7"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="D16" s="7"/>
-      <c r="K16" s="4"/>
-    </row>
-    <row r="17" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D17" s="3"/>
-      <c r="K17" s="7"/>
-    </row>
-    <row r="18" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D18" s="2"/>
-      <c r="K18" s="4"/>
-    </row>
-    <row r="19" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K19" s="7"/>
-    </row>
-    <row r="20" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K20" s="4"/>
-    </row>
-    <row r="21" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K21" s="7"/>
-    </row>
-    <row r="22" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K22" s="4"/>
-    </row>
-    <row r="23" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K23" s="7"/>
-    </row>
-    <row r="24" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K24" s="9"/>
-    </row>
-    <row r="25" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K25" s="7"/>
-    </row>
-    <row r="26" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K26" s="4"/>
-    </row>
-    <row r="27" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K27" s="7"/>
-    </row>
-    <row r="28" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K28" s="4"/>
-    </row>
-    <row r="29" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K29" s="6"/>
-    </row>
-    <row r="30" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K30" s="7"/>
-    </row>
-    <row r="31" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K31" s="9"/>
+    <row r="1" spans="1:5">
+      <c r="A1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" ht="15"/>
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:13">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+    </row>
+    <row r="4" ht="15" spans="1:13">
+      <c r="A4" s="7"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+    </row>
+    <row r="5" ht="15" spans="1:13">
+      <c r="A5" s="9"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+    </row>
+    <row r="6" ht="15" spans="1:13">
+      <c r="A6" s="7"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" ht="15" spans="1:13">
+      <c r="A7" s="10"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="9"/>
+      <c r="M7" s="12"/>
+    </row>
+    <row r="8" ht="15" spans="1:11">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="9"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="12"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" ht="15" spans="1:11">
+      <c r="A9" s="10"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="H9" s="13"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="6"/>
+    </row>
+    <row r="10" ht="15" spans="1:11">
+      <c r="A10" s="5"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="4"/>
+      <c r="H10" s="14"/>
+      <c r="K10" s="6"/>
+    </row>
+    <row r="11" ht="15" spans="1:11">
+      <c r="A11" s="14"/>
+      <c r="D11" s="6"/>
+      <c r="H11" s="11"/>
+      <c r="K11" s="9"/>
+    </row>
+    <row r="12" ht="15" spans="1:11">
+      <c r="A12" s="5"/>
+      <c r="D12" s="15"/>
+      <c r="K12" s="6"/>
+    </row>
+    <row r="13" ht="15" spans="1:11">
+      <c r="A13" s="10"/>
+      <c r="D13" s="5"/>
+      <c r="K13" s="12"/>
+    </row>
+    <row r="14" ht="15" spans="4:11">
+      <c r="D14" s="4"/>
+      <c r="K14" s="6"/>
+    </row>
+    <row r="15" ht="15" spans="4:11">
+      <c r="D15" s="6"/>
+      <c r="K15" s="9"/>
+    </row>
+    <row r="16" ht="15" spans="4:11">
+      <c r="D16" s="9"/>
+      <c r="K16" s="6"/>
+    </row>
+    <row r="17" ht="15" spans="4:11">
+      <c r="D17" s="5"/>
+      <c r="K17" s="9"/>
+    </row>
+    <row r="18" ht="15" spans="4:11">
+      <c r="D18" s="4"/>
+      <c r="K18" s="6"/>
+    </row>
+    <row r="19" ht="15" spans="11:11">
+      <c r="K19" s="9"/>
+    </row>
+    <row r="20" ht="15" spans="11:11">
+      <c r="K20" s="6"/>
+    </row>
+    <row r="21" ht="15" spans="11:11">
+      <c r="K21" s="9"/>
+    </row>
+    <row r="22" ht="15" spans="11:11">
+      <c r="K22" s="6"/>
+    </row>
+    <row r="23" ht="15" spans="11:11">
+      <c r="K23" s="9"/>
+    </row>
+    <row r="24" ht="15" spans="11:11">
+      <c r="K24" s="11"/>
+    </row>
+    <row r="25" ht="15" spans="11:11">
+      <c r="K25" s="9"/>
+    </row>
+    <row r="26" ht="15" spans="11:11">
+      <c r="K26" s="6"/>
+    </row>
+    <row r="27" ht="15" spans="11:11">
+      <c r="K27" s="9"/>
+    </row>
+    <row r="28" ht="15" spans="11:11">
+      <c r="K28" s="6"/>
+    </row>
+    <row r="29" ht="15" spans="11:11">
+      <c r="K29" s="8"/>
+    </row>
+    <row r="30" ht="15" spans="11:11">
+      <c r="K30" s="9"/>
+    </row>
+    <row r="31" ht="15" spans="11:11">
+      <c r="K31" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/24网络技术4班考勤.xlsx
+++ b/24网络技术4班考勤.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="21000" windowHeight="8580"/>
   </bookViews>
   <sheets>
     <sheet name="考勤" sheetId="3" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="120">
   <si>
     <t>学号</t>
   </si>
@@ -28,16 +28,34 @@
     <t>成绩</t>
   </si>
   <si>
+    <t>3.06理论</t>
+  </si>
+  <si>
+    <t>3.07理论</t>
+  </si>
+  <si>
+    <t>3.09理论</t>
+  </si>
+  <si>
+    <t>3.13理论</t>
+  </si>
+  <si>
+    <t>3.16理论</t>
+  </si>
+  <si>
+    <t>3.20理论</t>
+  </si>
+  <si>
     <t>黄泽屿</t>
   </si>
   <si>
     <t>×</t>
   </si>
   <si>
+    <t>√</t>
+  </si>
+  <si>
     <t>柳世康</t>
-  </si>
-  <si>
-    <t>√</t>
   </si>
   <si>
     <t>许文峥</t>
@@ -418,7 +436,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <color theme="6" tint="0.399639881588183"/>
+      <color theme="6" tint="0.399609363078707"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -437,7 +455,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="6" tint="0.399639881588183"/>
+      <color theme="6" tint="0.399609363078707"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1206,6 +1224,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1222,7 +1241,6 @@
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1544,7 +1562,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BM67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11.75" customWidth="1"/>
   </cols>
@@ -1560,547 +1578,781 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="15" spans="1:34">
+    <row r="2" ht="14.55" spans="1:34">
       <c r="A2" s="18"/>
       <c r="B2" s="18"/>
       <c r="C2" s="24"/>
-      <c r="D2">
-        <v>3.06</v>
-      </c>
-      <c r="E2">
-        <v>3.07</v>
-      </c>
-      <c r="F2">
-        <v>3.09</v>
-      </c>
-      <c r="O2" s="30"/>
-      <c r="AF2" s="31"/>
-      <c r="AH2" s="31"/>
-    </row>
-    <row r="3" ht="15.75" spans="1:6">
-      <c r="A3" s="25">
+      <c r="D2" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="31"/>
+      <c r="AF2" s="25"/>
+      <c r="AH2" s="25"/>
+    </row>
+    <row r="3" ht="15.9" spans="1:9">
+      <c r="A3" s="26">
         <v>2452020847</v>
       </c>
-      <c r="B3" s="26" t="s">
-        <v>3</v>
+      <c r="B3" s="27" t="s">
+        <v>9</v>
       </c>
       <c r="C3">
         <f>100-COUNTIF(D3:AZ3,"×")*3</f>
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" ht="15" spans="1:6">
-      <c r="A4" s="27">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" ht="15.15" spans="1:9">
+      <c r="A4" s="28">
         <v>2452020850</v>
       </c>
-      <c r="B4" s="26" t="s">
-        <v>5</v>
+      <c r="B4" s="27" t="s">
+        <v>12</v>
       </c>
       <c r="C4">
         <f t="shared" ref="C4:C63" si="0">100-COUNTIF(D4:AZ4,"×")*3</f>
         <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" ht="15" spans="1:6">
-      <c r="A5" s="27">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" ht="15.15" spans="1:9">
+      <c r="A5" s="28">
         <v>2452020851</v>
       </c>
-      <c r="B5" s="26" t="s">
-        <v>7</v>
+      <c r="B5" s="27" t="s">
+        <v>13</v>
       </c>
       <c r="C5">
         <f t="shared" si="0"/>
         <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" ht="15" spans="1:25">
-      <c r="A6" s="27">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" ht="15.15" spans="1:25">
+      <c r="A6" s="28">
         <v>2452020852</v>
       </c>
-      <c r="B6" s="26" t="s">
-        <v>8</v>
+      <c r="B6" s="27" t="s">
+        <v>14</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
         <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y6" s="31"/>
-    </row>
-    <row r="7" ht="15" spans="1:6">
-      <c r="A7" s="27">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y6" s="25"/>
+    </row>
+    <row r="7" ht="15.15" spans="1:9">
+      <c r="A7" s="28">
         <v>2452020854</v>
       </c>
-      <c r="B7" s="26" t="s">
-        <v>9</v>
+      <c r="B7" s="27" t="s">
+        <v>15</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
+        <v>91</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" ht="15.15" spans="1:9">
+      <c r="A8" s="28">
+        <v>2452020855</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" ht="15.15" spans="1:9">
+      <c r="A9" s="28">
+        <v>2452020858</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>91</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" ht="15.15" spans="1:9">
+      <c r="A10" s="28">
+        <v>2452020859</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" ht="15.15" spans="1:9">
+      <c r="A11" s="28">
+        <v>2452020863</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
         <v>97</v>
       </c>
-      <c r="D7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" ht="15" spans="1:6">
-      <c r="A8" s="27">
-        <v>2452020855</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8">
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" ht="15.15" spans="1:9">
+      <c r="A12" s="28">
+        <v>2452020864</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" ht="15.15" spans="1:9">
+      <c r="A13" s="28">
+        <v>2452020865</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="D8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" ht="15" spans="1:6">
-      <c r="A9" s="27">
-        <v>2452020858</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9">
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" ht="15.15" spans="1:9">
+      <c r="A14" s="28">
+        <v>2452020867</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" ht="15.15" spans="1:9">
+      <c r="A15" s="28">
+        <v>2452020869</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15">
         <f t="shared" si="0"/>
         <v>97</v>
       </c>
-      <c r="D9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" ht="15" spans="1:6">
-      <c r="A10" s="27">
-        <v>2452020859</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10">
-        <f t="shared" si="0"/>
-        <v>91</v>
-      </c>
-      <c r="D10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" ht="15" spans="1:6">
-      <c r="A11" s="27">
-        <v>2452020863</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" ht="15" spans="1:6">
-      <c r="A12" s="27">
-        <v>2452020864</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12">
-        <f t="shared" si="0"/>
-        <v>91</v>
-      </c>
-      <c r="D12" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" ht="15" spans="1:6">
-      <c r="A13" s="27">
-        <v>2452020865</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13">
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" ht="15.15" spans="1:9">
+      <c r="A16" s="26">
+        <v>2452020870</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" ht="15.15" spans="1:9">
+      <c r="A17" s="28">
+        <v>2452020873</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17">
         <f t="shared" si="0"/>
         <v>97</v>
       </c>
-      <c r="D13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" ht="15" spans="1:6">
-      <c r="A14" s="27">
-        <v>2452020867</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14">
-        <f t="shared" si="0"/>
-        <v>91</v>
-      </c>
-      <c r="D14" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" ht="15" spans="1:6">
-      <c r="A15" s="27">
-        <v>2452020869</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" ht="15" spans="1:6">
-      <c r="A16" s="25">
-        <v>2452020870</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D16" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" ht="15" spans="1:6">
-      <c r="A17" s="27">
-        <v>2452020873</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
       <c r="D17" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F17" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="27">
+        <v>11</v>
+      </c>
+      <c r="G17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" ht="15.15" spans="1:9">
+      <c r="A18" s="28">
         <v>2452020877</v>
       </c>
-      <c r="B18" s="26" t="s">
-        <v>20</v>
+      <c r="B18" s="27" t="s">
+        <v>26</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" ht="15" spans="1:6">
-      <c r="A19" s="27">
+        <v>11</v>
+      </c>
+      <c r="G18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" ht="15.15" spans="1:9">
+      <c r="A19" s="28">
         <v>2452020878</v>
       </c>
-      <c r="B19" s="26" t="s">
-        <v>21</v>
+      <c r="B19" s="27" t="s">
+        <v>27</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" ht="15" spans="1:6">
-      <c r="A20" s="27">
+        <v>11</v>
+      </c>
+      <c r="G19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" t="s">
+        <v>10</v>
+      </c>
+      <c r="I19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" ht="15.15" spans="1:9">
+      <c r="A20" s="28">
         <v>2452020879</v>
       </c>
-      <c r="B20" s="26" t="s">
-        <v>22</v>
+      <c r="B20" s="27" t="s">
+        <v>28</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" ht="15" spans="1:6">
-      <c r="A21" s="27">
+        <v>11</v>
+      </c>
+      <c r="G20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" ht="15.15" spans="1:9">
+      <c r="A21" s="28">
         <v>2452020881</v>
       </c>
-      <c r="B21" s="26" t="s">
-        <v>23</v>
+      <c r="B21" s="27" t="s">
+        <v>29</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E21" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" ht="15" spans="1:6">
-      <c r="A22" s="27">
+        <v>10</v>
+      </c>
+      <c r="G21" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" ht="15.15" spans="1:9">
+      <c r="A22" s="28">
         <v>2452020882</v>
       </c>
-      <c r="B22" s="26" t="s">
-        <v>24</v>
+      <c r="B22" s="27" t="s">
+        <v>30</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D22" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" ht="15" spans="1:6">
-      <c r="A23" s="27">
+        <v>10</v>
+      </c>
+      <c r="G22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" ht="15.15" spans="1:9">
+      <c r="A23" s="28">
         <v>2452020889</v>
       </c>
-      <c r="B23" s="26" t="s">
-        <v>25</v>
+      <c r="B23" s="27" t="s">
+        <v>31</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D23" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E23" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" ht="15" spans="1:6">
-      <c r="A24" s="27">
+        <v>10</v>
+      </c>
+      <c r="G23" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" t="s">
+        <v>10</v>
+      </c>
+      <c r="I23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" ht="15.15" spans="1:9">
+      <c r="A24" s="28">
         <v>2452020899</v>
       </c>
-      <c r="B24" s="26" t="s">
-        <v>26</v>
+      <c r="B24" s="27" t="s">
+        <v>32</v>
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
+        <v>94</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" ht="15.15" spans="1:9">
+      <c r="A25" s="28">
+        <v>2452020906</v>
+      </c>
+      <c r="B25" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+      <c r="D25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25" t="s">
+        <v>10</v>
+      </c>
+      <c r="I25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" ht="15.15" spans="1:9">
+      <c r="A26" s="28">
+        <v>2452020909</v>
+      </c>
+      <c r="B26" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="0"/>
         <v>97</v>
       </c>
-      <c r="D24" t="s">
-        <v>6</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" ht="15" spans="1:6">
-      <c r="A25" s="27">
-        <v>2452020906</v>
-      </c>
-      <c r="B25" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25">
-        <f t="shared" si="0"/>
-        <v>91</v>
-      </c>
-      <c r="D25" t="s">
-        <v>4</v>
-      </c>
-      <c r="E25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F25" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" ht="15" spans="1:6">
-      <c r="A26" s="27">
-        <v>2452020909</v>
-      </c>
-      <c r="B26" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
       <c r="D26" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F26" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" s="23" customFormat="1" ht="15" spans="1:35">
-      <c r="A27" s="27">
+        <v>11</v>
+      </c>
+      <c r="G26" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" t="s">
+        <v>10</v>
+      </c>
+      <c r="I26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" s="23" customFormat="1" ht="15.15" spans="1:35">
+      <c r="A27" s="28">
         <v>2452020910</v>
       </c>
-      <c r="B27" s="26" t="s">
-        <v>29</v>
+      <c r="B27" s="27" t="s">
+        <v>35</v>
       </c>
       <c r="C27">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D27" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F27" t="s">
-        <v>6</v>
+        <v>11</v>
+      </c>
+      <c r="G27" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" t="s">
+        <v>11</v>
       </c>
       <c r="M27"/>
       <c r="N27"/>
@@ -2126,790 +2378,1114 @@
       <c r="AH27"/>
       <c r="AI27"/>
     </row>
-    <row r="28" ht="15" spans="1:6">
-      <c r="A28" s="25">
+    <row r="28" ht="15.15" spans="1:9">
+      <c r="A28" s="26">
         <v>2452020911</v>
       </c>
-      <c r="B28" s="26" t="s">
-        <v>30</v>
+      <c r="B28" s="27" t="s">
+        <v>36</v>
       </c>
       <c r="C28">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D28" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E28" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F28" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" ht="15" spans="1:6">
-      <c r="A29" s="25">
+        <v>11</v>
+      </c>
+      <c r="G28" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" t="s">
+        <v>10</v>
+      </c>
+      <c r="I28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" ht="15.15" spans="1:9">
+      <c r="A29" s="26">
         <v>2452020917</v>
       </c>
-      <c r="B29" s="26" t="s">
-        <v>31</v>
+      <c r="B29" s="27" t="s">
+        <v>37</v>
       </c>
       <c r="C29">
         <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+      <c r="D29" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" t="s">
+        <v>10</v>
+      </c>
+      <c r="I29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" ht="15.15" spans="1:9">
+      <c r="A30" s="28">
+        <v>2452020919</v>
+      </c>
+      <c r="B30" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="D30" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" t="s">
+        <v>10</v>
+      </c>
+      <c r="H30" t="s">
+        <v>10</v>
+      </c>
+      <c r="I30" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" ht="15.15" spans="1:9">
+      <c r="A31" s="28">
+        <v>2452020920</v>
+      </c>
+      <c r="B31" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+      <c r="D31" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" t="s">
+        <v>10</v>
+      </c>
+      <c r="I31" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" ht="15.15" spans="1:9">
+      <c r="A32" s="28">
+        <v>2452020922</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="D32" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" ht="15.15" spans="1:9">
+      <c r="A33" s="28">
+        <v>2452020924</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" t="s">
+        <v>10</v>
+      </c>
+      <c r="I33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" ht="15.15" spans="1:9">
+      <c r="A34" s="28">
+        <v>2452020927</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+      <c r="D34" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" t="s">
+        <v>10</v>
+      </c>
+      <c r="H34" t="s">
+        <v>10</v>
+      </c>
+      <c r="I34" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" ht="15.15" spans="1:9">
+      <c r="A35" s="28">
+        <v>2452020928</v>
+      </c>
+      <c r="B35" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="0"/>
         <v>97</v>
       </c>
-      <c r="D29" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" ht="15" spans="1:6">
-      <c r="A30" s="27">
-        <v>2452020919</v>
-      </c>
-      <c r="B30" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30">
-        <f t="shared" si="0"/>
-        <v>94</v>
-      </c>
-      <c r="D30" t="s">
-        <v>4</v>
-      </c>
-      <c r="E30" t="s">
-        <v>4</v>
-      </c>
-      <c r="F30" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" ht="15" spans="1:6">
-      <c r="A31" s="27">
-        <v>2452020920</v>
-      </c>
-      <c r="B31" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C31">
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" t="s">
+        <v>11</v>
+      </c>
+      <c r="G35" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" t="s">
+        <v>10</v>
+      </c>
+      <c r="I35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" ht="15.15" spans="1:9">
+      <c r="A36" s="28">
+        <v>2452020931</v>
+      </c>
+      <c r="B36" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="0"/>
+        <v>97</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36" t="s">
+        <v>11</v>
+      </c>
+      <c r="H36" t="s">
+        <v>10</v>
+      </c>
+      <c r="I36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" ht="15.15" spans="1:9">
+      <c r="A37" s="28">
+        <v>2452020932</v>
+      </c>
+      <c r="B37" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="0"/>
+        <v>97</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" t="s">
+        <v>11</v>
+      </c>
+      <c r="G37" t="s">
+        <v>11</v>
+      </c>
+      <c r="H37" t="s">
+        <v>10</v>
+      </c>
+      <c r="I37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" ht="15.15" spans="1:9">
+      <c r="A38" s="28">
+        <v>2452020934</v>
+      </c>
+      <c r="B38" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" t="s">
+        <v>10</v>
+      </c>
+      <c r="H38" t="s">
+        <v>10</v>
+      </c>
+      <c r="I38" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" ht="15.15" spans="1:9">
+      <c r="A39" s="28">
+        <v>2452020935</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="0"/>
+        <v>97</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" t="s">
+        <v>11</v>
+      </c>
+      <c r="G39" t="s">
+        <v>11</v>
+      </c>
+      <c r="H39" t="s">
+        <v>11</v>
+      </c>
+      <c r="I39" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" ht="15.15" spans="1:9">
+      <c r="A40" s="28">
+        <v>2452020937</v>
+      </c>
+      <c r="B40" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="0"/>
+        <v>97</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H40" t="s">
+        <v>11</v>
+      </c>
+      <c r="I40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" ht="15.15" spans="1:9">
+      <c r="A41" s="28">
+        <v>2452020939</v>
+      </c>
+      <c r="B41" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+      <c r="D41" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" t="s">
+        <v>10</v>
+      </c>
+      <c r="H41" t="s">
+        <v>10</v>
+      </c>
+      <c r="I41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" ht="15.15" spans="1:9">
+      <c r="A42" s="26">
+        <v>2452020940</v>
+      </c>
+      <c r="B42" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="D31" t="s">
-        <v>4</v>
-      </c>
-      <c r="E31" t="s">
-        <v>4</v>
-      </c>
-      <c r="F31" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" ht="15" spans="1:6">
-      <c r="A32" s="27">
-        <v>2452020922</v>
-      </c>
-      <c r="B32" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32">
-        <f t="shared" si="0"/>
-        <v>94</v>
-      </c>
-      <c r="D32" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" t="s">
-        <v>4</v>
-      </c>
-      <c r="F32" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" ht="15" spans="1:6">
-      <c r="A33" s="27">
-        <v>2452020924</v>
-      </c>
-      <c r="B33" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33">
-        <f t="shared" si="0"/>
-        <v>94</v>
-      </c>
-      <c r="D33" t="s">
-        <v>6</v>
-      </c>
-      <c r="E33" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" ht="15" spans="1:6">
-      <c r="A34" s="27">
-        <v>2452020927</v>
-      </c>
-      <c r="B34" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C34">
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" t="s">
+        <v>11</v>
+      </c>
+      <c r="H42" t="s">
+        <v>10</v>
+      </c>
+      <c r="I42" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" ht="15.15" spans="1:9">
+      <c r="A43" s="28">
+        <v>2452020941</v>
+      </c>
+      <c r="B43" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="D34" t="s">
-        <v>4</v>
-      </c>
-      <c r="E34" t="s">
-        <v>4</v>
-      </c>
-      <c r="F34" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" ht="15" spans="1:6">
-      <c r="A35" s="27">
-        <v>2452020928</v>
-      </c>
-      <c r="B35" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="C35">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D35" t="s">
-        <v>6</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="27">
-        <v>2452020931</v>
-      </c>
-      <c r="B36" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D36" t="s">
-        <v>6</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" ht="15" spans="1:6">
-      <c r="A37" s="27">
-        <v>2452020932</v>
-      </c>
-      <c r="B37" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C37">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D37" t="s">
-        <v>6</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" ht="15" spans="1:6">
-      <c r="A38" s="27">
-        <v>2452020934</v>
-      </c>
-      <c r="B38" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C38">
-        <f t="shared" si="0"/>
-        <v>94</v>
-      </c>
-      <c r="D38" t="s">
-        <v>6</v>
-      </c>
-      <c r="E38" t="s">
-        <v>4</v>
-      </c>
-      <c r="F38" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" ht="15" spans="1:6">
-      <c r="A39" s="27">
-        <v>2452020935</v>
-      </c>
-      <c r="B39" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D39" t="s">
-        <v>6</v>
-      </c>
-      <c r="E39" t="s">
-        <v>6</v>
-      </c>
-      <c r="F39" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" ht="15" spans="1:6">
-      <c r="A40" s="27">
-        <v>2452020937</v>
-      </c>
-      <c r="B40" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C40">
-        <f t="shared" si="0"/>
-        <v>97</v>
-      </c>
-      <c r="D40" t="s">
-        <v>6</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" ht="15" spans="1:6">
-      <c r="A41" s="27">
-        <v>2452020939</v>
-      </c>
-      <c r="B41" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C41">
-        <f t="shared" si="0"/>
-        <v>91</v>
-      </c>
-      <c r="D41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E41" t="s">
-        <v>4</v>
-      </c>
-      <c r="F41" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" ht="15" spans="1:6">
-      <c r="A42" s="25">
-        <v>2452020940</v>
-      </c>
-      <c r="B42" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C42">
-        <f t="shared" si="0"/>
-        <v>97</v>
-      </c>
-      <c r="D42" t="s">
-        <v>6</v>
-      </c>
-      <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" ht="15" spans="1:6">
-      <c r="A43" s="27">
-        <v>2452020941</v>
-      </c>
-      <c r="B43" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C43">
-        <f t="shared" si="0"/>
-        <v>97</v>
-      </c>
       <c r="D43" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E43" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F43" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" ht="15" spans="1:6">
-      <c r="A44" s="27">
+        <v>10</v>
+      </c>
+      <c r="G43" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" t="s">
+        <v>10</v>
+      </c>
+      <c r="I43" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" ht="15.15" spans="1:9">
+      <c r="A44" s="28">
         <v>2452020942</v>
       </c>
-      <c r="B44" s="26" t="s">
-        <v>46</v>
+      <c r="B44" s="27" t="s">
+        <v>52</v>
       </c>
       <c r="C44">
         <f t="shared" si="0"/>
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D44" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" ht="15" spans="1:6">
-      <c r="A45" s="27">
+        <v>10</v>
+      </c>
+      <c r="G44" t="s">
+        <v>10</v>
+      </c>
+      <c r="H44" t="s">
+        <v>10</v>
+      </c>
+      <c r="I44" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" ht="15.15" spans="1:9">
+      <c r="A45" s="28">
         <v>2452020945</v>
       </c>
-      <c r="B45" s="26" t="s">
-        <v>47</v>
+      <c r="B45" s="27" t="s">
+        <v>53</v>
       </c>
       <c r="C45">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D45" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E45" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F45" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" ht="15" spans="1:6">
-      <c r="A46" s="27">
+        <v>11</v>
+      </c>
+      <c r="G45" t="s">
+        <v>11</v>
+      </c>
+      <c r="H45" t="s">
+        <v>11</v>
+      </c>
+      <c r="I45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" ht="15.15" spans="1:9">
+      <c r="A46" s="28">
         <v>2452020949</v>
       </c>
-      <c r="B46" s="26" t="s">
-        <v>48</v>
+      <c r="B46" s="27" t="s">
+        <v>54</v>
       </c>
       <c r="C46">
         <f>110-COUNTIF(D46:AZ46,"×")*3</f>
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D46" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E46" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F46" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" ht="15" spans="1:6">
-      <c r="A47" s="27">
+        <v>11</v>
+      </c>
+      <c r="G46" t="s">
+        <v>11</v>
+      </c>
+      <c r="H46" t="s">
+        <v>11</v>
+      </c>
+      <c r="I46" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" ht="15.15" spans="1:9">
+      <c r="A47" s="28">
         <v>2452020950</v>
       </c>
-      <c r="B47" s="26" t="s">
-        <v>49</v>
+      <c r="B47" s="27" t="s">
+        <v>55</v>
       </c>
       <c r="C47">
         <f t="shared" si="0"/>
         <v>97</v>
       </c>
       <c r="D47" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E47" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F47" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" ht="15" spans="1:6">
-      <c r="A48" s="27">
+        <v>10</v>
+      </c>
+      <c r="G47" t="s">
+        <v>11</v>
+      </c>
+      <c r="H47" t="s">
+        <v>11</v>
+      </c>
+      <c r="I47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" ht="15.15" spans="1:9">
+      <c r="A48" s="28">
         <v>2452020953</v>
       </c>
-      <c r="B48" s="26" t="s">
-        <v>50</v>
+      <c r="B48" s="27" t="s">
+        <v>56</v>
       </c>
       <c r="C48">
         <f t="shared" si="0"/>
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D48" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E48" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F48" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" ht="15" spans="1:6">
-      <c r="A49" s="27">
+        <v>10</v>
+      </c>
+      <c r="G48" t="s">
+        <v>10</v>
+      </c>
+      <c r="H48" t="s">
+        <v>10</v>
+      </c>
+      <c r="I48" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" ht="15.15" spans="1:9">
+      <c r="A49" s="28">
         <v>2452020955</v>
       </c>
-      <c r="B49" s="26" t="s">
-        <v>51</v>
+      <c r="B49" s="27" t="s">
+        <v>57</v>
       </c>
       <c r="C49">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D49" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E49" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F49" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" ht="15" spans="1:6">
-      <c r="A50" s="27">
+        <v>11</v>
+      </c>
+      <c r="G49" t="s">
+        <v>11</v>
+      </c>
+      <c r="H49" t="s">
+        <v>11</v>
+      </c>
+      <c r="I49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" ht="15.15" spans="1:9">
+      <c r="A50" s="28">
         <v>2452020958</v>
       </c>
-      <c r="B50" s="26" t="s">
-        <v>52</v>
+      <c r="B50" s="27" t="s">
+        <v>58</v>
       </c>
       <c r="C50">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D50" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E50" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F50" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" ht="15" spans="1:6">
-      <c r="A51" s="27">
+        <v>11</v>
+      </c>
+      <c r="G50" t="s">
+        <v>10</v>
+      </c>
+      <c r="H50" t="s">
+        <v>10</v>
+      </c>
+      <c r="I50" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" ht="15.15" spans="1:9">
+      <c r="A51" s="28">
         <v>2452020963</v>
       </c>
-      <c r="B51" s="26" t="s">
-        <v>53</v>
+      <c r="B51" s="27" t="s">
+        <v>59</v>
       </c>
       <c r="C51">
         <f t="shared" si="0"/>
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D51" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E51" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52" ht="15" spans="1:6">
-      <c r="A52" s="27">
+        <v>10</v>
+      </c>
+      <c r="G51" t="s">
+        <v>10</v>
+      </c>
+      <c r="H51" t="s">
+        <v>10</v>
+      </c>
+      <c r="I51" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" ht="15.15" spans="1:9">
+      <c r="A52" s="28">
         <v>2452020966</v>
       </c>
-      <c r="B52" s="26" t="s">
-        <v>54</v>
+      <c r="B52" s="27" t="s">
+        <v>60</v>
       </c>
       <c r="C52">
         <f t="shared" si="0"/>
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D52" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E52" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" ht="15" spans="1:6">
-      <c r="A53" s="28">
+        <v>10</v>
+      </c>
+      <c r="G52" t="s">
+        <v>10</v>
+      </c>
+      <c r="H52" t="s">
+        <v>10</v>
+      </c>
+      <c r="I52" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" ht="15.15" spans="1:9">
+      <c r="A53" s="29">
         <v>2452020968</v>
       </c>
-      <c r="B53" s="29" t="s">
-        <v>55</v>
+      <c r="B53" s="30" t="s">
+        <v>61</v>
       </c>
       <c r="C53">
         <f t="shared" si="0"/>
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D53" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E53" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F53" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="54" ht="15" spans="1:6">
-      <c r="A54" s="27">
+        <v>10</v>
+      </c>
+      <c r="G53" t="s">
+        <v>10</v>
+      </c>
+      <c r="H53" t="s">
+        <v>10</v>
+      </c>
+      <c r="I53" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" ht="15.15" spans="1:9">
+      <c r="A54" s="28">
         <v>2452020970</v>
       </c>
-      <c r="B54" s="26" t="s">
-        <v>56</v>
+      <c r="B54" s="27" t="s">
+        <v>62</v>
       </c>
       <c r="C54">
         <f t="shared" si="0"/>
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D54" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E54" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F54" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" ht="15" spans="1:6">
-      <c r="A55" s="25">
+        <v>10</v>
+      </c>
+      <c r="G54" t="s">
+        <v>10</v>
+      </c>
+      <c r="H54" t="s">
+        <v>10</v>
+      </c>
+      <c r="I54" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" ht="15.15" spans="1:9">
+      <c r="A55" s="26">
         <v>2452020972</v>
       </c>
-      <c r="B55" s="26" t="s">
-        <v>57</v>
+      <c r="B55" s="27" t="s">
+        <v>63</v>
       </c>
       <c r="C55">
         <f t="shared" si="0"/>
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D55" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E55" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" ht="15" spans="1:6">
-      <c r="A56" s="27">
+        <v>10</v>
+      </c>
+      <c r="G55" t="s">
+        <v>10</v>
+      </c>
+      <c r="H55" t="s">
+        <v>10</v>
+      </c>
+      <c r="I55" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" ht="15.15" spans="1:9">
+      <c r="A56" s="28">
         <v>2452020974</v>
       </c>
-      <c r="B56" s="26" t="s">
-        <v>58</v>
+      <c r="B56" s="27" t="s">
+        <v>64</v>
       </c>
       <c r="C56">
         <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+      <c r="D56" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" t="s">
+        <v>10</v>
+      </c>
+      <c r="G56" t="s">
+        <v>10</v>
+      </c>
+      <c r="H56" t="s">
+        <v>10</v>
+      </c>
+      <c r="I56" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" ht="15.15" spans="1:9">
+      <c r="A57" s="28">
+        <v>2452020977</v>
+      </c>
+      <c r="B57" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="C57">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+      <c r="D57" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" t="s">
+        <v>10</v>
+      </c>
+      <c r="G57" t="s">
+        <v>10</v>
+      </c>
+      <c r="H57" t="s">
+        <v>10</v>
+      </c>
+      <c r="I57" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" ht="15.15" spans="1:9">
+      <c r="A58" s="28">
+        <v>2452020981</v>
+      </c>
+      <c r="B58" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="C58">
+        <f t="shared" si="0"/>
         <v>97</v>
       </c>
-      <c r="D56" t="s">
-        <v>6</v>
-      </c>
-      <c r="E56" t="s">
-        <v>6</v>
-      </c>
-      <c r="F56" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57" ht="15" spans="1:6">
-      <c r="A57" s="27">
-        <v>2452020977</v>
-      </c>
-      <c r="B57" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="C57">
-        <f t="shared" si="0"/>
-        <v>91</v>
-      </c>
-      <c r="D57" t="s">
-        <v>4</v>
-      </c>
-      <c r="E57" t="s">
-        <v>4</v>
-      </c>
-      <c r="F57" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" ht="15" spans="1:6">
-      <c r="A58" s="27">
-        <v>2452020981</v>
-      </c>
-      <c r="B58" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="C58">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
       <c r="D58" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E58" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F58" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" ht="15" spans="1:6">
-      <c r="A59" s="27">
+        <v>11</v>
+      </c>
+      <c r="G58" t="s">
+        <v>11</v>
+      </c>
+      <c r="H58" t="s">
+        <v>11</v>
+      </c>
+      <c r="I58" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" ht="15.15" spans="1:9">
+      <c r="A59" s="28">
         <v>2452020983</v>
       </c>
-      <c r="B59" s="26" t="s">
-        <v>61</v>
+      <c r="B59" s="27" t="s">
+        <v>67</v>
       </c>
       <c r="C59">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D59" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E59" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F59" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" ht="15" spans="1:6">
-      <c r="A60" s="27">
+        <v>10</v>
+      </c>
+      <c r="G59" t="s">
+        <v>10</v>
+      </c>
+      <c r="H59" t="s">
+        <v>10</v>
+      </c>
+      <c r="I59" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" ht="15.15" spans="1:9">
+      <c r="A60" s="28">
         <v>2452021017</v>
       </c>
-      <c r="B60" s="26" t="s">
-        <v>62</v>
+      <c r="B60" s="27" t="s">
+        <v>68</v>
       </c>
       <c r="C60">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D60" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E60" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F60" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" ht="15" spans="1:6">
-      <c r="A61" s="27">
+        <v>10</v>
+      </c>
+      <c r="G60" t="s">
+        <v>10</v>
+      </c>
+      <c r="H60" t="s">
+        <v>10</v>
+      </c>
+      <c r="I60" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" ht="15.15" spans="1:9">
+      <c r="A61" s="28">
         <v>2452021026</v>
       </c>
-      <c r="B61" s="26" t="s">
-        <v>63</v>
+      <c r="B61" s="27" t="s">
+        <v>69</v>
       </c>
       <c r="C61">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D61" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E61" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F61" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="62" ht="15" spans="1:6">
-      <c r="A62" s="27">
+        <v>10</v>
+      </c>
+      <c r="G61" t="s">
+        <v>10</v>
+      </c>
+      <c r="H61" t="s">
+        <v>10</v>
+      </c>
+      <c r="I61" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" ht="15.15" spans="1:9">
+      <c r="A62" s="28">
         <v>2452021389</v>
       </c>
-      <c r="B62" s="26" t="s">
-        <v>64</v>
+      <c r="B62" s="27" t="s">
+        <v>70</v>
       </c>
       <c r="C62">
         <f t="shared" si="0"/>
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D62" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E62" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F62" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" ht="15" spans="1:6">
-      <c r="A63" s="27">
+        <v>10</v>
+      </c>
+      <c r="G62" t="s">
+        <v>10</v>
+      </c>
+      <c r="H62" t="s">
+        <v>10</v>
+      </c>
+      <c r="I62" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" ht="15.15" spans="1:9">
+      <c r="A63" s="28">
         <v>2452021400</v>
       </c>
-      <c r="B63" s="26" t="s">
-        <v>65</v>
+      <c r="B63" s="27" t="s">
+        <v>71</v>
       </c>
       <c r="C63">
         <f t="shared" si="0"/>
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D63" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E63" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F63" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="64" ht="15" spans="1:2">
+        <v>10</v>
+      </c>
+      <c r="G63" t="s">
+        <v>10</v>
+      </c>
+      <c r="H63" t="s">
+        <v>10</v>
+      </c>
+      <c r="I63" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" ht="14.55" spans="1:2">
       <c r="A64" s="12"/>
       <c r="B64" s="12"/>
     </row>
     <row r="65" ht="78" customHeight="1" spans="4:65">
       <c r="D65">
-        <f>COUNTIF(D3:D49,"×")</f>
-        <v>17</v>
+        <f>COUNTIF(D3:D63,"×")</f>
+        <v>26</v>
       </c>
       <c r="E65">
-        <f t="shared" ref="E65:BM65" si="1">COUNTIF(E3:E49,"×")</f>
-        <v>23</v>
+        <f t="shared" ref="E65:AU65" si="1">COUNTIF(E3:E63,"×")</f>
+        <v>32</v>
       </c>
       <c r="F65">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G65">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H65">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="I65">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J65">
         <f t="shared" si="1"/>
@@ -3064,81 +3640,81 @@
         <v>0</v>
       </c>
       <c r="AV65">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="AV65:BM65" si="2">COUNTIF(AV3:AV49,"×")</f>
         <v>0</v>
       </c>
       <c r="AW65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AX65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AY65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AZ65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BA65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BB65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BC65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BD65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BE65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BF65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BG65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BH65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BI65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BJ65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BK65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BL65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BM65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="67" ht="30" spans="8:15">
       <c r="H67" s="32" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
@@ -3185,7 +3761,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -3196,10 +3772,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="4"/>
   <cols>
-    <col min="3" max="3" width="15.625" customWidth="1"/>
-    <col min="4" max="5" width="11.125" customWidth="1"/>
+    <col min="3" max="3" width="15.6296296296296" customWidth="1"/>
+    <col min="4" max="5" width="11.1296296296296" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3208,7 +3784,7 @@
       </c>
       <c r="B1" s="17"/>
     </row>
-    <row r="2" ht="15" spans="1:5">
+    <row r="2" ht="14.55" spans="1:5">
       <c r="A2" s="18"/>
       <c r="B2" s="19" t="s">
         <v>2</v>
@@ -3217,9 +3793,9 @@
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
     </row>
-    <row r="3" ht="24.75" spans="1:4">
+    <row r="3" ht="24.3" spans="1:4">
       <c r="A3" s="12" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B3" s="21">
         <f>100-COUNTIF(C3:AZ3,"△")*30</f>
@@ -3228,9 +3804,9 @@
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
     </row>
-    <row r="4" ht="24" spans="1:4">
+    <row r="4" ht="23.55" spans="1:4">
       <c r="A4" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B4" s="21">
         <f t="shared" ref="B4:B49" si="0">100-COUNTIF(C4:AZ4,"△")*30</f>
@@ -3239,9 +3815,9 @@
       <c r="C4" s="22"/>
       <c r="D4" s="22"/>
     </row>
-    <row r="5" ht="24" spans="1:5">
+    <row r="5" ht="23.55" spans="1:5">
       <c r="A5" s="12" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B5" s="21">
         <f t="shared" si="0"/>
@@ -3251,9 +3827,9 @@
       <c r="D5" s="22"/>
       <c r="E5" s="22"/>
     </row>
-    <row r="6" ht="24" spans="1:4">
+    <row r="6" ht="23.55" spans="1:4">
       <c r="A6" s="11" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B6" s="21">
         <f t="shared" si="0"/>
@@ -3262,27 +3838,27 @@
       <c r="C6" s="22"/>
       <c r="D6" s="22"/>
     </row>
-    <row r="7" ht="15" spans="1:2">
+    <row r="7" ht="14.55" spans="1:2">
       <c r="A7" s="12" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B7" s="21">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
     </row>
-    <row r="8" ht="15" spans="1:2">
+    <row r="8" ht="14.55" spans="1:2">
       <c r="A8" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B8" s="21">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
     </row>
-    <row r="9" ht="24" spans="1:4">
+    <row r="9" ht="23.55" spans="1:4">
       <c r="A9" s="12" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B9" s="21">
         <f t="shared" si="0"/>
@@ -3290,9 +3866,9 @@
       </c>
       <c r="D9" s="22"/>
     </row>
-    <row r="10" ht="24" spans="1:4">
+    <row r="10" ht="23.55" spans="1:4">
       <c r="A10" s="11" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B10" s="21">
         <f t="shared" si="0"/>
@@ -3301,9 +3877,9 @@
       <c r="C10" s="22"/>
       <c r="D10" s="22"/>
     </row>
-    <row r="11" ht="24" spans="1:5">
+    <row r="11" ht="23.55" spans="1:5">
       <c r="A11" s="14" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B11" s="21">
         <f t="shared" si="0"/>
@@ -3313,9 +3889,9 @@
       <c r="D11" s="22"/>
       <c r="E11" s="22"/>
     </row>
-    <row r="12" ht="24" spans="1:4">
+    <row r="12" ht="23.55" spans="1:4">
       <c r="A12" s="11" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B12" s="21">
         <f t="shared" si="0"/>
@@ -3323,9 +3899,9 @@
       </c>
       <c r="D12" s="22"/>
     </row>
-    <row r="13" ht="24" spans="1:4">
+    <row r="13" ht="23.55" spans="1:4">
       <c r="A13" s="12" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B13" s="21">
         <f t="shared" si="0"/>
@@ -3333,9 +3909,9 @@
       </c>
       <c r="D13" s="22"/>
     </row>
-    <row r="14" ht="24" spans="1:4">
+    <row r="14" ht="23.55" spans="1:4">
       <c r="A14" s="11" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B14" s="21">
         <f t="shared" si="0"/>
@@ -3343,9 +3919,9 @@
       </c>
       <c r="D14" s="22"/>
     </row>
-    <row r="15" ht="24" spans="1:4">
+    <row r="15" ht="23.55" spans="1:4">
       <c r="A15" s="12" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B15" s="21">
         <f t="shared" si="0"/>
@@ -3353,9 +3929,9 @@
       </c>
       <c r="D15" s="22"/>
     </row>
-    <row r="16" ht="24" spans="1:5">
+    <row r="16" ht="23.55" spans="1:5">
       <c r="A16" s="11" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B16" s="21">
         <f t="shared" si="0"/>
@@ -3365,9 +3941,9 @@
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
     </row>
-    <row r="17" ht="24" spans="1:4">
+    <row r="17" ht="23.55" spans="1:4">
       <c r="A17" s="12" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B17" s="21">
         <f t="shared" si="0"/>
@@ -3375,9 +3951,9 @@
       </c>
       <c r="D17" s="22"/>
     </row>
-    <row r="18" ht="24" spans="1:4">
+    <row r="18" ht="23.55" spans="1:4">
       <c r="A18" s="11" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B18" s="21">
         <f t="shared" si="0"/>
@@ -3385,9 +3961,9 @@
       </c>
       <c r="D18" s="22"/>
     </row>
-    <row r="19" ht="24" spans="1:5">
+    <row r="19" ht="23.55" spans="1:5">
       <c r="A19" s="12" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B19" s="21">
         <f t="shared" si="0"/>
@@ -3397,9 +3973,9 @@
       <c r="D19" s="22"/>
       <c r="E19" s="22"/>
     </row>
-    <row r="20" ht="24" spans="1:4">
+    <row r="20" ht="23.55" spans="1:4">
       <c r="A20" s="11" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B20" s="21">
         <f t="shared" si="0"/>
@@ -3407,9 +3983,9 @@
       </c>
       <c r="D20" s="22"/>
     </row>
-    <row r="21" ht="24" spans="1:4">
+    <row r="21" ht="23.55" spans="1:4">
       <c r="A21" s="12" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B21" s="21">
         <f t="shared" si="0"/>
@@ -3417,27 +3993,27 @@
       </c>
       <c r="D21" s="22"/>
     </row>
-    <row r="22" ht="15" spans="1:2">
+    <row r="22" ht="14.55" spans="1:2">
       <c r="A22" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B22" s="21">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
     </row>
-    <row r="23" ht="15" spans="1:2">
+    <row r="23" ht="14.55" spans="1:2">
       <c r="A23" s="12" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B23" s="21">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
     </row>
-    <row r="24" ht="24" spans="1:5">
+    <row r="24" ht="23.55" spans="1:5">
       <c r="A24" s="11" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B24" s="21">
         <f t="shared" si="0"/>
@@ -3447,9 +4023,9 @@
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
     </row>
-    <row r="25" ht="24" spans="1:5">
+    <row r="25" ht="23.55" spans="1:5">
       <c r="A25" s="12" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B25" s="21">
         <f t="shared" si="0"/>
@@ -3459,9 +4035,9 @@
       <c r="D25" s="22"/>
       <c r="E25" s="22"/>
     </row>
-    <row r="26" ht="24" spans="1:5">
+    <row r="26" ht="23.55" spans="1:5">
       <c r="A26" s="11" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B26" s="21">
         <f t="shared" si="0"/>
@@ -3471,9 +4047,9 @@
       <c r="D26" s="22"/>
       <c r="E26" s="22"/>
     </row>
-    <row r="27" ht="24" spans="1:5">
+    <row r="27" ht="23.55" spans="1:5">
       <c r="A27" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B27" s="21">
         <f t="shared" si="0"/>
@@ -3483,27 +4059,27 @@
       <c r="D27" s="22"/>
       <c r="E27" s="22"/>
     </row>
-    <row r="28" ht="15" spans="1:2">
+    <row r="28" ht="14.55" spans="1:2">
       <c r="A28" s="11" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B28" s="21">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
     </row>
-    <row r="29" ht="15" spans="1:2">
+    <row r="29" ht="14.55" spans="1:2">
       <c r="A29" s="12" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B29" s="21">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
     </row>
-    <row r="30" ht="24" spans="1:5">
+    <row r="30" ht="23.55" spans="1:5">
       <c r="A30" s="11" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B30" s="21">
         <f t="shared" si="0"/>
@@ -3513,9 +4089,9 @@
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
     </row>
-    <row r="31" ht="24" spans="1:5">
+    <row r="31" ht="23.55" spans="1:5">
       <c r="A31" s="12" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B31" s="21">
         <f t="shared" si="0"/>
@@ -3525,9 +4101,9 @@
       <c r="D31" s="22"/>
       <c r="E31" s="22"/>
     </row>
-    <row r="32" ht="24" spans="1:4">
+    <row r="32" ht="23.55" spans="1:4">
       <c r="A32" s="11" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B32" s="21">
         <f t="shared" si="0"/>
@@ -3536,9 +4112,9 @@
       <c r="C32" s="22"/>
       <c r="D32" s="22"/>
     </row>
-    <row r="33" ht="24" spans="1:3">
+    <row r="33" ht="23.55" spans="1:3">
       <c r="A33" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B33" s="21">
         <f t="shared" si="0"/>
@@ -3546,9 +4122,9 @@
       </c>
       <c r="C33" s="22"/>
     </row>
-    <row r="34" ht="24" spans="1:5">
+    <row r="34" ht="23.55" spans="1:5">
       <c r="A34" s="11" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B34" s="21">
         <f t="shared" si="0"/>
@@ -3558,9 +4134,9 @@
       <c r="D34" s="22"/>
       <c r="E34" s="22"/>
     </row>
-    <row r="35" ht="24" spans="1:5">
+    <row r="35" ht="23.55" spans="1:5">
       <c r="A35" s="12" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B35" s="21">
         <f t="shared" si="0"/>
@@ -3570,18 +4146,18 @@
       <c r="D35" s="22"/>
       <c r="E35" s="22"/>
     </row>
-    <row r="36" ht="15" spans="1:2">
+    <row r="36" ht="14.55" spans="1:2">
       <c r="A36" s="11" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B36" s="21">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
     </row>
-    <row r="37" ht="24" spans="1:5">
+    <row r="37" ht="23.55" spans="1:5">
       <c r="A37" s="12" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B37" s="21">
         <f t="shared" si="0"/>
@@ -3590,9 +4166,9 @@
       <c r="D37" s="22"/>
       <c r="E37" s="22"/>
     </row>
-    <row r="38" ht="24" spans="1:5">
+    <row r="38" ht="23.55" spans="1:5">
       <c r="A38" s="11" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B38" s="21">
         <f t="shared" si="0"/>
@@ -3602,9 +4178,9 @@
       <c r="D38" s="22"/>
       <c r="E38" s="22"/>
     </row>
-    <row r="39" ht="24" spans="1:5">
+    <row r="39" ht="23.55" spans="1:5">
       <c r="A39" s="12" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B39" s="21">
         <f t="shared" si="0"/>
@@ -3614,9 +4190,9 @@
       <c r="D39" s="22"/>
       <c r="E39" s="22"/>
     </row>
-    <row r="40" ht="24" spans="1:5">
+    <row r="40" ht="23.55" spans="1:5">
       <c r="A40" s="11" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B40" s="21">
         <f t="shared" si="0"/>
@@ -3626,9 +4202,9 @@
       <c r="D40" s="22"/>
       <c r="E40" s="22"/>
     </row>
-    <row r="41" ht="24" spans="1:4">
+    <row r="41" ht="23.55" spans="1:4">
       <c r="A41" s="12" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B41" s="21">
         <f t="shared" si="0"/>
@@ -3636,9 +4212,9 @@
       </c>
       <c r="D41" s="22"/>
     </row>
-    <row r="42" ht="24" spans="1:5">
+    <row r="42" ht="23.55" spans="1:5">
       <c r="A42" s="11" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B42" s="21">
         <f t="shared" si="0"/>
@@ -3648,18 +4224,18 @@
       <c r="D42" s="22"/>
       <c r="E42" s="22"/>
     </row>
-    <row r="43" ht="15" spans="1:2">
+    <row r="43" ht="14.55" spans="1:2">
       <c r="A43" s="12" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B43" s="21">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
     </row>
-    <row r="44" ht="24" spans="1:5">
+    <row r="44" ht="23.55" spans="1:5">
       <c r="A44" s="11" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B44" s="21">
         <f t="shared" si="0"/>
@@ -3669,9 +4245,9 @@
       <c r="D44" s="22"/>
       <c r="E44" s="22"/>
     </row>
-    <row r="45" ht="24" spans="1:5">
+    <row r="45" ht="23.55" spans="1:5">
       <c r="A45" s="12" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B45" s="21">
         <f t="shared" si="0"/>
@@ -3681,9 +4257,9 @@
       <c r="D45" s="22"/>
       <c r="E45" s="22"/>
     </row>
-    <row r="46" ht="24" spans="1:5">
+    <row r="46" ht="23.55" spans="1:5">
       <c r="A46" s="11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B46" s="21">
         <f t="shared" si="0"/>
@@ -3693,9 +4269,9 @@
       <c r="D46" s="22"/>
       <c r="E46" s="22"/>
     </row>
-    <row r="47" ht="24" spans="1:5">
+    <row r="47" ht="23.55" spans="1:5">
       <c r="A47" s="12" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B47" s="21">
         <f t="shared" si="0"/>
@@ -3705,18 +4281,18 @@
       <c r="D47" s="22"/>
       <c r="E47" s="22"/>
     </row>
-    <row r="48" ht="15" spans="1:2">
+    <row r="48" ht="14.55" spans="1:2">
       <c r="A48" s="11" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B48" s="21">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
     </row>
-    <row r="49" ht="15" spans="1:2">
+    <row r="49" ht="14.55" spans="1:2">
       <c r="A49" s="12" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B49" s="21">
         <f t="shared" si="0"/>
@@ -3737,7 +4313,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="2"/>
@@ -3746,8 +4322,8 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" ht="15"/>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:13">
+    <row r="2" ht="14.55"/>
+    <row r="3" s="1" customFormat="1" ht="14.55" spans="1:13">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="5"/>
@@ -3762,7 +4338,7 @@
       <c r="L3" s="11"/>
       <c r="M3" s="11"/>
     </row>
-    <row r="4" ht="15" spans="1:13">
+    <row r="4" ht="14.55" spans="1:13">
       <c r="A4" s="7"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -3777,7 +4353,7 @@
       <c r="L4" s="12"/>
       <c r="M4" s="12"/>
     </row>
-    <row r="5" ht="15" spans="1:13">
+    <row r="5" ht="14.55" spans="1:13">
       <c r="A5" s="9"/>
       <c r="B5" s="10"/>
       <c r="C5" s="4"/>
@@ -3792,7 +4368,7 @@
       <c r="L5" s="11"/>
       <c r="M5" s="11"/>
     </row>
-    <row r="6" ht="15" spans="1:13">
+    <row r="6" ht="14.55" spans="1:13">
       <c r="A6" s="7"/>
       <c r="B6" s="5"/>
       <c r="C6" s="6"/>
@@ -3807,7 +4383,7 @@
       <c r="L6" s="12"/>
       <c r="M6" s="12"/>
     </row>
-    <row r="7" ht="15" spans="1:13">
+    <row r="7" ht="14.55" spans="1:13">
       <c r="A7" s="10"/>
       <c r="C7" s="4"/>
       <c r="D7" s="11"/>
@@ -3820,7 +4396,7 @@
       <c r="K7" s="9"/>
       <c r="M7" s="12"/>
     </row>
-    <row r="8" ht="15" spans="1:11">
+    <row r="8" ht="14.55" spans="1:11">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="D8" s="4"/>
@@ -3830,7 +4406,7 @@
       <c r="J8" s="13"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" ht="15" spans="1:11">
+    <row r="9" ht="14.55" spans="1:11">
       <c r="A9" s="10"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
@@ -3838,86 +4414,86 @@
       <c r="J9" s="12"/>
       <c r="K9" s="6"/>
     </row>
-    <row r="10" ht="15" spans="1:11">
+    <row r="10" ht="14.55" spans="1:11">
       <c r="A10" s="5"/>
       <c r="D10" s="9"/>
       <c r="E10" s="4"/>
       <c r="H10" s="14"/>
       <c r="K10" s="6"/>
     </row>
-    <row r="11" ht="15" spans="1:11">
+    <row r="11" ht="14.55" spans="1:11">
       <c r="A11" s="14"/>
       <c r="D11" s="6"/>
       <c r="H11" s="11"/>
       <c r="K11" s="9"/>
     </row>
-    <row r="12" ht="15" spans="1:11">
+    <row r="12" ht="14.55" spans="1:11">
       <c r="A12" s="5"/>
       <c r="D12" s="15"/>
       <c r="K12" s="6"/>
     </row>
-    <row r="13" ht="15" spans="1:11">
+    <row r="13" ht="14.55" spans="1:11">
       <c r="A13" s="10"/>
       <c r="D13" s="5"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" ht="15" spans="4:11">
+    <row r="14" ht="14.55" spans="4:11">
       <c r="D14" s="4"/>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" ht="15" spans="4:11">
+    <row r="15" ht="14.55" spans="4:11">
       <c r="D15" s="6"/>
       <c r="K15" s="9"/>
     </row>
-    <row r="16" ht="15" spans="4:11">
+    <row r="16" ht="14.55" spans="4:11">
       <c r="D16" s="9"/>
       <c r="K16" s="6"/>
     </row>
-    <row r="17" ht="15" spans="4:11">
+    <row r="17" ht="14.55" spans="4:11">
       <c r="D17" s="5"/>
       <c r="K17" s="9"/>
     </row>
-    <row r="18" ht="15" spans="4:11">
+    <row r="18" ht="14.55" spans="4:11">
       <c r="D18" s="4"/>
       <c r="K18" s="6"/>
     </row>
-    <row r="19" ht="15" spans="11:11">
+    <row r="19" ht="14.55" spans="11:11">
       <c r="K19" s="9"/>
     </row>
-    <row r="20" ht="15" spans="11:11">
+    <row r="20" ht="14.55" spans="11:11">
       <c r="K20" s="6"/>
     </row>
-    <row r="21" ht="15" spans="11:11">
+    <row r="21" ht="14.55" spans="11:11">
       <c r="K21" s="9"/>
     </row>
-    <row r="22" ht="15" spans="11:11">
+    <row r="22" ht="14.55" spans="11:11">
       <c r="K22" s="6"/>
     </row>
-    <row r="23" ht="15" spans="11:11">
+    <row r="23" ht="14.55" spans="11:11">
       <c r="K23" s="9"/>
     </row>
-    <row r="24" ht="15" spans="11:11">
+    <row r="24" ht="14.55" spans="11:11">
       <c r="K24" s="11"/>
     </row>
-    <row r="25" ht="15" spans="11:11">
+    <row r="25" ht="14.55" spans="11:11">
       <c r="K25" s="9"/>
     </row>
-    <row r="26" ht="15" spans="11:11">
+    <row r="26" ht="14.55" spans="11:11">
       <c r="K26" s="6"/>
     </row>
-    <row r="27" ht="15" spans="11:11">
+    <row r="27" ht="14.55" spans="11:11">
       <c r="K27" s="9"/>
     </row>
-    <row r="28" ht="15" spans="11:11">
+    <row r="28" ht="14.55" spans="11:11">
       <c r="K28" s="6"/>
     </row>
-    <row r="29" ht="15" spans="11:11">
+    <row r="29" ht="14.55" spans="11:11">
       <c r="K29" s="8"/>
     </row>
-    <row r="30" ht="15" spans="11:11">
+    <row r="30" ht="14.55" spans="11:11">
       <c r="K30" s="9"/>
     </row>
-    <row r="31" ht="15" spans="11:11">
+    <row r="31" ht="14.55" spans="11:11">
       <c r="K31" s="11"/>
     </row>
   </sheetData>
